--- a/data/trans_orig/IP31KM05_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP31KM05_2023-Clase-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>142</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>99949</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>91748</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>107782</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>82,46%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>75,69%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>88,92%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>119</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>76779</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>66690</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>83741</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>75,49%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>65,57%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>82,33%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>142</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>112325</t>
+          <t>77718</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>102909</t>
+          <t>69958</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>119660</t>
+          <t>84558</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>83,1%</t>
+          <t>77,45%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>76,13%</t>
+          <t>69,72%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>88,52%</t>
+          <t>84,26%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>189104</t>
+          <t>177667</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>175288</t>
+          <t>166037</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>199786</t>
+          <t>187416</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>79,83%</t>
+          <t>80,19%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>74,0%</t>
+          <t>74,94%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>84,34%</t>
+          <t>84,59%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>21260</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>13427</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>29461</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>17,54%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>11,08%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>24,31%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>24930</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>17968</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>35019</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>24,51%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>17,67%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>34,43%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>22851</t>
+          <t>22631</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>15516</t>
+          <t>15791</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>32267</t>
+          <t>30391</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>16,9%</t>
+          <t>22,55%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>15,74%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>23,87%</t>
+          <t>30,28%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>47782</t>
+          <t>43891</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>37100</t>
+          <t>34142</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>61598</t>
+          <t>55521</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>20,17%</t>
+          <t>19,81%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>15,66%</t>
+          <t>15,41%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>26,0%</t>
+          <t>25,06%</t>
         </is>
       </c>
     </row>
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>167</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>121209</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>121209</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>121209</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>152</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>101709</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>101709</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>101709</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>167</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>135176</t>
+          <t>100349</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>135176</t>
+          <t>100349</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>135176</t>
+          <t>100349</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>236886</t>
+          <t>221558</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>236886</t>
+          <t>221558</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>236886</t>
+          <t>221558</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,72 +1063,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>73696</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>66623</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>79044</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>81,99%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>74,12%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>87,94%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>118</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>80908</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>74658</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>85588</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>86,63%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>79,94%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>91,64%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>104</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>76293</t>
+          <t>82585</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>68393</t>
+          <t>75770</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>82787</t>
+          <t>87442</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>81,42%</t>
+          <t>86,56%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>72,98%</t>
+          <t>79,42%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>88,35%</t>
+          <t>91,65%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>157202</t>
+          <t>156281</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>147694</t>
+          <t>146854</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>165408</t>
+          <t>163990</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>84,02%</t>
+          <t>84,34%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>78,94%</t>
+          <t>79,26%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>88,41%</t>
+          <t>88,5%</t>
         </is>
       </c>
     </row>
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>16184</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>10836</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>23257</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>18,01%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>12,06%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>25,88%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>12484</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>7804</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>18734</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>13,37%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>8,36%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>20,06%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>17415</t>
+          <t>12825</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>10921</t>
+          <t>7968</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>25315</t>
+          <t>19640</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>13,44%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>27,02%</t>
+          <t>20,58%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>29899</t>
+          <t>29009</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>21693</t>
+          <t>21300</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>39407</t>
+          <t>38436</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>15,66%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>21,06%</t>
+          <t>20,74%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>89880</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>89880</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>89880</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>138</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>93392</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>93392</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>93392</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>127</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>93708</t>
+          <t>95410</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>93708</t>
+          <t>95410</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>93708</t>
+          <t>95410</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>187101</t>
+          <t>185290</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>187101</t>
+          <t>185290</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>187101</t>
+          <t>185290</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,72 +1406,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>45353</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>39657</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>49484</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>81,21%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>71,01%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>88,61%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>56</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>38136</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>32207</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>43090</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>76,14%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>64,3%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>86,03%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>48514</t>
+          <t>39801</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>41392</t>
+          <t>32717</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>53910</t>
+          <t>44772</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>77,83%</t>
+          <t>76,53%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>66,4%</t>
+          <t>62,91%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>86,49%</t>
+          <t>86,08%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>86650</t>
+          <t>85154</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>76935</t>
+          <t>75946</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>93676</t>
+          <t>91734</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>77,08%</t>
+          <t>78,95%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>68,43%</t>
+          <t>70,42%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>83,33%</t>
+          <t>85,05%</t>
         </is>
       </c>
     </row>
@@ -1519,72 +1519,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>10491</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>6360</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>16187</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>18,79%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>11,39%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>28,99%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>11953</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>6999</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>17882</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>23,86%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>13,97%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>35,7%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>13820</t>
+          <t>12209</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>8424</t>
+          <t>7238</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>20942</t>
+          <t>19293</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>22,17%</t>
+          <t>23,47%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>13,92%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>33,6%</t>
+          <t>37,09%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>25772</t>
+          <t>22700</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>18746</t>
+          <t>16120</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>35487</t>
+          <t>31908</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>22,92%</t>
+          <t>21,05%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>14,95%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>31,57%</t>
+          <t>29,58%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>55844</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>55844</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>55844</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>71</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>50089</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>50089</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>50089</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>62334</t>
+          <t>52010</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>62334</t>
+          <t>52010</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>62334</t>
+          <t>52010</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>112422</t>
+          <t>107854</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>112422</t>
+          <t>107854</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>112422</t>
+          <t>107854</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,72 +1749,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>233</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>171060</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>161844</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>178769</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>86,69%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>82,02%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>90,6%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>208</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>170118</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>156110</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>186991</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>78,93%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>72,43%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>86,76%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>233</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>183761</t>
+          <t>133979</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>173309</t>
+          <t>124166</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>191669</t>
+          <t>143178</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>86,41%</t>
+          <t>75,85%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>81,5%</t>
+          <t>70,29%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>90,13%</t>
+          <t>81,06%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>353880</t>
+          <t>305040</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>337732</t>
+          <t>291887</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>370272</t>
+          <t>316537</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>82,64%</t>
+          <t>81,57%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>78,87%</t>
+          <t>78,05%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>86,47%</t>
+          <t>84,65%</t>
         </is>
       </c>
     </row>
@@ -1862,72 +1862,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>26253</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>18544</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>35469</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>13,31%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>9,4%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>17,98%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>63</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>45419</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>28546</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>59427</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>21,07%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>13,24%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>27,57%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>28897</t>
+          <t>42661</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>20989</t>
+          <t>33462</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>39349</t>
+          <t>52474</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>13,59%</t>
+          <t>24,15%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>18,94%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>18,5%</t>
+          <t>29,71%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>74316</t>
+          <t>68913</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>57924</t>
+          <t>57416</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>90464</t>
+          <t>82066</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>17,36%</t>
+          <t>18,43%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>15,35%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>21,13%</t>
+          <t>21,95%</t>
         </is>
       </c>
     </row>
@@ -1975,57 +1975,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>273</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>197313</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>197313</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>197313</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>271</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>215537</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>215537</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>215537</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>273</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>212658</t>
+          <t>176640</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>212658</t>
+          <t>176640</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>212658</t>
+          <t>176640</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>428196</t>
+          <t>373953</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>428196</t>
+          <t>373953</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>428196</t>
+          <t>373953</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2092,72 +2092,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>110015</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>98882</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>119644</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>75,57%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>67,92%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>82,18%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>139</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>95307</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>86844</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>101253</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>82,51%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>75,18%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>87,66%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>144</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>118736</t>
+          <t>95107</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>105475</t>
+          <t>87273</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>129075</t>
+          <t>101028</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>74,46%</t>
+          <t>82,37%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>66,14%</t>
+          <t>75,58%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>80,94%</t>
+          <t>87,5%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>214043</t>
+          <t>205122</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>199417</t>
+          <t>192883</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>227008</t>
+          <t>217023</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>77,84%</t>
+          <t>78,58%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>72,52%</t>
+          <t>73,89%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>82,56%</t>
+          <t>83,13%</t>
         </is>
       </c>
     </row>
@@ -2205,72 +2205,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>35571</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>25942</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>46704</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>24,43%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>17,82%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>32,08%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>20202</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>14256</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>28665</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>17,49%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>12,34%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>24,82%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>40725</t>
+          <t>20359</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>30386</t>
+          <t>14438</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>53986</t>
+          <t>28193</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>25,54%</t>
+          <t>17,63%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>33,86%</t>
+          <t>24,42%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>60927</t>
+          <t>55930</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>47962</t>
+          <t>44029</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>75553</t>
+          <t>68169</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>22,16%</t>
+          <t>21,42%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>17,44%</t>
+          <t>16,87%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>27,48%</t>
+          <t>26,11%</t>
         </is>
       </c>
     </row>
@@ -2318,57 +2318,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>192</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>145586</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>145586</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>145586</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>171</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>115509</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>115509</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>115509</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>192</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>159461</t>
+          <t>115466</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>159461</t>
+          <t>115466</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>159461</t>
+          <t>115466</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>274970</t>
+          <t>261052</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>274970</t>
+          <t>261052</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>274970</t>
+          <t>261052</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2435,72 +2435,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>56431</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>49393</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>60931</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>85,68%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>74,99%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>92,51%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>83</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>58256</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>52675</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>62636</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>84,56%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>76,46%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>90,92%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>58456</t>
+          <t>59376</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>51266</t>
+          <t>53575</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>63192</t>
+          <t>63661</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>84,68%</t>
+          <t>84,39%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>74,27%</t>
+          <t>76,15%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>91,54%</t>
+          <t>90,48%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>116711</t>
+          <t>115808</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>107835</t>
+          <t>107485</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>123666</t>
+          <t>121778</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>84,62%</t>
+          <t>85,02%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>78,18%</t>
+          <t>78,91%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>89,66%</t>
+          <t>89,4%</t>
         </is>
       </c>
     </row>
@@ -2548,72 +2548,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>9432</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>4932</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>16470</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>14,32%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>7,49%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>25,01%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>10639</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>6259</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>16220</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>15,44%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>9,08%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>23,54%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>10575</t>
+          <t>10980</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>5839</t>
+          <t>6695</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>17765</t>
+          <t>16781</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>15,61%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>25,73%</t>
+          <t>23,85%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>21214</t>
+          <t>20412</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>14259</t>
+          <t>14442</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>30090</t>
+          <t>28735</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>14,98%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>21,82%</t>
+          <t>21,09%</t>
         </is>
       </c>
     </row>
@@ -2661,57 +2661,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>65863</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>65863</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>65863</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>99</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>68895</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>68895</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>68895</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>69031</t>
+          <t>70356</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>69031</t>
+          <t>70356</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>69031</t>
+          <t>70356</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>137925</t>
+          <t>136220</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>137925</t>
+          <t>136220</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>137925</t>
+          <t>136220</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2778,72 +2778,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>756</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>556505</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>536581</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>572998</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>82,36%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>79,41%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>84,8%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>723</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>519505</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>499111</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>539624</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>80,53%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>77,37%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>83,65%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>756</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>598085</t>
+          <t>488567</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>575557</t>
+          <t>469959</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>616575</t>
+          <t>504849</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>81,66%</t>
+          <t>80,06%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>78,59%</t>
+          <t>77,01%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>84,19%</t>
+          <t>82,73%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>1117589</t>
+          <t>1045072</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1087303</t>
+          <t>1019837</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1145215</t>
+          <t>1068510</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>81,13%</t>
+          <t>81,27%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>78,93%</t>
+          <t>79,31%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>83,14%</t>
+          <t>83,09%</t>
         </is>
       </c>
     </row>
@@ -2891,72 +2891,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>167</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>119190</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>102697</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>139114</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>17,64%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>15,2%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>20,59%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>179</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>125626</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>105507</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>146020</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>19,47%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>16,35%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>22,63%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>167</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>134283</t>
+          <t>121665</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>115793</t>
+          <t>105383</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>156811</t>
+          <t>140273</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>18,34%</t>
+          <t>19,94%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>15,81%</t>
+          <t>17,27%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>21,41%</t>
+          <t>22,99%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>259910</t>
+          <t>240855</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>232284</t>
+          <t>217417</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>290196</t>
+          <t>266090</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>18,87%</t>
+          <t>18,73%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>16,91%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>21,07%</t>
+          <t>20,69%</t>
         </is>
       </c>
     </row>
@@ -3004,57 +3004,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>923</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>675695</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>675695</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>675695</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>902</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>645131</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>645131</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>645131</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>923</t>
-        </is>
-      </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>732368</t>
+          <t>610232</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>732368</t>
+          <t>610232</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>732368</t>
+          <t>610232</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1377499</t>
+          <t>1285927</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1377499</t>
+          <t>1285927</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1377499</t>
+          <t>1285927</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
